--- a/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR VALVULA NOVO 18_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/RETENTOR VALVULA NOVO 18_02.xlsx
@@ -374,7 +374,9 @@
       <c r="C4" s="2">
         <v>30.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>20.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
